--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/GEORGIA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/GEORGIA_2010.xlsx
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C176">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C207">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C754">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C850">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C851">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C881">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C888">
@@ -23748,7 +23748,7 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1300">
@@ -26610,7 +26610,7 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1459">
